--- a/grupos/1FM - Estadisticos 20211.xlsx
+++ b/grupos/1FM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -158,15 +158,15 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -188,31 +188,115 @@
     <t>ABAD</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
     <t>AVELLEIRA</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>FRANCO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
+    <t>XOCUA</t>
   </si>
   <si>
     <t>SOL</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>CASTELLANOS</t>
@@ -221,157 +305,73 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>MARITZA</t>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>DEBORA GEORGINA</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
+    <t>CRISTINA KARELY</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DARLET VICTORIA</t>
+  </si>
+  <si>
+    <t>CRISTIAN MANUEL</t>
+  </si>
+  <si>
     <t>JONATHAN MOISES</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>JOCELIN</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUZ AMELY</t>
+  </si>
+  <si>
+    <t>SAORI</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>AMIR ALONSO</t>
+  </si>
+  <si>
     <t>NOEMI</t>
   </si>
   <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>DEBORA GEORGINA</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>CRISTINA KARELY</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DARLET VICTORIA</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
-    <t>SAORI</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>AMIR ALONSO</t>
   </si>
   <si>
     <t>PAULA MARIA</t>
@@ -866,25 +866,25 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -920,16 +920,16 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -958,19 +958,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -994,7 +994,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1003,10 +1003,10 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1020,31 +1020,31 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1071,19 +1071,19 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1112,19 +1112,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1148,19 +1148,19 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1189,19 +1189,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1225,7 +1225,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1234,10 +1234,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1266,10 +1266,10 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1343,19 +1343,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1379,19 +1379,19 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1405,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1420,19 +1420,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1456,13 +1456,13 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1497,19 +1497,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1574,19 +1574,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1613,7 +1613,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1651,19 +1651,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1687,7 +1687,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1713,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1728,19 +1728,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1764,13 +1764,13 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1805,19 +1805,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1841,16 +1841,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1882,19 +1882,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1924,13 +1924,13 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1959,16 +1959,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1995,16 +1995,16 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2036,19 +2036,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2081,10 +2081,10 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2113,19 +2113,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2152,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2161,7 +2161,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2190,19 +2190,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2229,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2267,19 +2267,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2306,16 +2306,16 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2344,19 +2344,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2380,10 +2380,10 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2421,19 +2421,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2463,13 +2463,13 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2486,7 +2486,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>7</v>
@@ -2498,19 +2498,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2534,16 +2534,16 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2560,7 +2560,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2575,16 +2575,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2614,13 +2614,13 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2652,19 +2652,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2697,7 +2697,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2765,30 +2765,30 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>20.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2797,30 +2797,30 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2829,19 +2829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2861,25 +2861,25 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2896,22 +2896,22 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>95.83</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2953,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2988,236 +2988,16 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920331</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920331</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920331</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920332</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920332</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920332</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920337</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920342</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920352</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920353</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3259,13 +3039,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3273,95 +3053,95 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920337</v>
+        <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920342</v>
+        <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920352</v>
+        <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920353</v>
+        <v>21330051920336</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920333</v>
+        <v>21330051920337</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>101</v>
@@ -3372,13 +3152,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920334</v>
+        <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>102</v>
@@ -3389,13 +3169,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920335</v>
+        <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>103</v>
@@ -3406,13 +3186,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920336</v>
+        <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>104</v>
@@ -3423,13 +3203,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920338</v>
+        <v>21330051920341</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
@@ -3440,13 +3220,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920339</v>
+        <v>21330051920342</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>106</v>
@@ -3457,13 +3237,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920340</v>
+        <v>21330051920343</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -3474,13 +3254,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920341</v>
+        <v>21330051920344</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3491,13 +3271,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920343</v>
+        <v>21330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3508,13 +3288,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920344</v>
+        <v>21330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3525,13 +3305,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920345</v>
+        <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3542,13 +3322,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920346</v>
+        <v>21330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3559,13 +3339,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920347</v>
+        <v>21330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -3576,13 +3356,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920348</v>
+        <v>21330051920350</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>114</v>
@@ -3593,13 +3373,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920349</v>
+        <v>21330051920351</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -3610,13 +3390,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920350</v>
+        <v>21330051920352</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>116</v>
@@ -3627,13 +3407,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920351</v>
+        <v>21330051920353</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
         <v>117</v>
@@ -3647,10 +3427,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
         <v>118</v>
@@ -3698,48 +3478,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920342</v>
+        <v>21330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920352</v>
+        <v>21330051920347</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3747,13 +3527,13 @@
         <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3762,7 +3542,7 @@
         <v>45</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1FM - Estadisticos 20211.xlsx
+++ b/grupos/1FM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -878,7 +878,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -955,7 +955,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -991,7 +991,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1032,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -1109,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -1186,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -1263,7 +1263,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>10</v>
@@ -1299,7 +1299,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -1376,7 +1376,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1417,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -1494,7 +1494,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1725,7 +1725,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -1802,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -1956,7 +1956,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -2033,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -2110,7 +2110,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2187,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>10</v>
@@ -2264,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>10</v>
@@ -2300,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2341,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2377,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2418,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2495,7 +2495,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2572,7 +2572,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2608,7 +2608,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2649,7 +2649,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2797,16 +2797,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -3446,7 +3446,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3478,16 +3478,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920337</v>
+        <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3501,16 +3501,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920347</v>
+        <v>21330051920353</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -3524,24 +3524,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920353</v>
+        <v>21330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920347</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
         <v>45</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20211.xlsx
+++ b/grupos/1FM - Estadisticos 20211.xlsx
@@ -1429,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>6</v>

--- a/grupos/1FM - Estadisticos 20211.xlsx
+++ b/grupos/1FM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -155,24 +155,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Moreno Arollo Anél</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Moreno Arollo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,124 +188,124 @@
     <t>ABAD</t>
   </si>
   <si>
+    <t>AVELLEIRA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
-  </si>
-  <si>
-    <t>AVELLEIRA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ISRAEL</t>
@@ -869,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -887,46 +887,46 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -973,22 +973,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1047,43 +1047,43 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1127,22 +1127,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1151,10 +1151,10 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1204,34 +1204,34 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1272,46 +1272,46 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1358,22 +1358,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1382,16 +1382,16 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1435,31 +1435,31 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1512,22 +1512,22 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1589,22 +1589,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1613,16 +1613,16 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1666,22 +1666,22 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1690,10 +1690,10 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1743,22 +1743,22 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1773,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1820,22 +1820,22 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1850,7 +1850,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1897,22 +1897,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1924,7 +1924,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -1971,25 +1971,25 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -1998,13 +1998,13 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2051,40 +2051,40 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2128,22 +2128,22 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2152,13 +2152,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2205,37 +2205,37 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2282,22 +2282,22 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2309,13 +2309,13 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2359,40 +2359,40 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>6</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2436,22 +2436,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2513,22 +2513,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2537,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2546,7 +2546,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2587,31 +2587,31 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2620,10 +2620,10 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2667,22 +2667,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -2765,19 +2765,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="G2">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2797,16 +2797,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2829,19 +2829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2861,30 +2861,30 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,19 +2893,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2953,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2978,26 +2978,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3039,13 +3019,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3053,10 +3033,10 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
         <v>96</v>
@@ -3070,10 +3050,10 @@
         <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
         <v>97</v>
@@ -3087,10 +3067,10 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
@@ -3104,10 +3084,10 @@
         <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
         <v>99</v>
@@ -3121,10 +3101,10 @@
         <v>21330051920336</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>100</v>
@@ -3138,10 +3118,10 @@
         <v>21330051920337</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
         <v>101</v>
@@ -3155,10 +3135,10 @@
         <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
         <v>102</v>
@@ -3172,10 +3152,10 @@
         <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>103</v>
@@ -3189,10 +3169,10 @@
         <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>104</v>
@@ -3206,10 +3186,10 @@
         <v>21330051920341</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
@@ -3223,10 +3203,10 @@
         <v>21330051920342</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>106</v>
@@ -3240,10 +3220,10 @@
         <v>21330051920343</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -3257,10 +3237,10 @@
         <v>21330051920344</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3274,10 +3254,10 @@
         <v>21330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3291,10 +3271,10 @@
         <v>21330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3308,10 +3288,10 @@
         <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3325,10 +3305,10 @@
         <v>21330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3342,10 +3322,10 @@
         <v>21330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -3359,10 +3339,10 @@
         <v>21330051920350</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
         <v>114</v>
@@ -3376,10 +3356,10 @@
         <v>21330051920351</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -3393,10 +3373,10 @@
         <v>21330051920352</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>116</v>
@@ -3410,10 +3390,10 @@
         <v>21330051920353</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>117</v>
@@ -3427,10 +3407,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>118</v>
@@ -3446,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3481,16 +3461,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>46</v>
@@ -3504,16 +3484,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
         <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -3524,47 +3504,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920337</v>
+        <v>21330051920331</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920347</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>
